--- a/output/pdf_financials_xlsx/AMC.xlsx
+++ b/output/pdf_financials_xlsx/AMC.xlsx
@@ -3679,28 +3679,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.100036</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.104608</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.03878</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.191031</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.928679</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.363279</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.735695</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.142512</v>
       </c>
     </row>
     <row r="93">
@@ -5921,7 +5921,11 @@
           <t>Reserves (notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -6308,7 +6312,11 @@
           <t>Reserves (notes 7, 8 and 9)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6615,7 +6623,11 @@
           <t>Reserves (notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -6800,7 +6812,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -7367,7 +7383,11 @@
           <t>Reserves (Note 3)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AMC.xlsx
+++ b/output/pdf_financials_xlsx/AMC.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.000389</v>
+        <v>0.014539</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.001749</v>
+        <v>0.116898</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.465262</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.000389</v>
+        <v>-0.014539</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.001749</v>
+        <v>-0.116898</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.465262</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008477</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.2272</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>1.819722</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.903931</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.562485</v>
       </c>
     </row>
     <row r="13">
@@ -1388,7 +1388,7 @@
         <v>-0.014539</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.014539</v>
+        <v>-0.006062</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.260609</v>
@@ -1400,16 +1400,16 @@
         <v>-19.617091</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-24.514748</v>
+        <v>-24.741948</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-24.348031</v>
+        <v>-26.167753</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-24.734572</v>
+        <v>-25.638503</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-19.096893</v>
+        <v>-19.659378</v>
       </c>
     </row>
     <row r="28">
@@ -1456,7 +1456,7 @@
         <v>-0.014539</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.014539</v>
+        <v>-0.006062</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.260609</v>
@@ -1468,16 +1468,16 @@
         <v>-19.617091</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24.494433</v>
+        <v>-24.721633</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-24.285457</v>
+        <v>-26.105179</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-24.670985</v>
+        <v>-25.574916</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-19.0483</v>
+        <v>-19.610785</v>
       </c>
     </row>
     <row r="30">
@@ -1632,31 +1632,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.212182</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.858862</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.611891</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.88593</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>55.774455</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.958183</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.550399</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.355813</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.55628</v>
       </c>
     </row>
     <row r="35">
@@ -1700,31 +1700,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.212182</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.858862</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.611891</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.88593</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>55.774455</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.958183</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.550399</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.355813</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.55628</v>
       </c>
     </row>
     <row r="37">
@@ -2108,31 +2108,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.212182</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.858862</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.268751</v>
+        <v>0.65686</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.635319</v>
+        <v>0.749389</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>57.042924</v>
+        <v>1.268469</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>52.936896</v>
+        <v>45.978713</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>30.521184</v>
+        <v>29.970785</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.596905</v>
+        <v>34.241092</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>17.026868</v>
+        <v>16.470588</v>
       </c>
     </row>
     <row r="49">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12967,14 +12967,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.014539</v>
+        <v>0.014539</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.116898</v>
+        <v>0.116898</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -13530,11 +13530,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>-0.014539</v>
+        <v>0.014539</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AMC.xlsx
+++ b/output/pdf_financials_xlsx/AMC.xlsx
@@ -10595,7 +10595,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>0.235001</v>
       </c>
